--- a/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 5,5</t>
+          <t>-10,02; 5,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 0,0</t>
+          <t>-16,42; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,56</t>
+          <t>-4,75; 2,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,0</t>
+          <t>-9,36; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -1,16</t>
+          <t>-9,81; -1,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -1,69</t>
+          <t>-10,04; -1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 4,37</t>
+          <t>-2,07; 4,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,16</t>
+          <t>-3,25; 2,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,83</t>
+          <t>-4,42; 0,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; -0,32</t>
+          <t>-5,53; -0,43</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,39</t>
+          <t>-100,0; -0,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 23,04</t>
+          <t>-100,0; -19,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,2; 41,28</t>
+          <t>-78,72; 50,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,15; 1,25</t>
+          <t>-92,63; -2,58</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 3,39</t>
+          <t>-15,4; 4,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 0,49</t>
+          <t>-17,61; 1,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 0,0</t>
+          <t>-9,83; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,68</t>
+          <t>-5,92; 3,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,52</t>
+          <t>-7,57; 1,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1,4</t>
+          <t>-7,72; 1,48</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 271,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 270,22</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -0,62</t>
+          <t>-7,56; -0,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -1,65</t>
+          <t>-7,94; -1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,82</t>
+          <t>-2,53; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,42</t>
+          <t>-3,36; 1,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,17</t>
+          <t>-3,96; 0,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,55</t>
+          <t>-4,39; -0,56</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 0,29</t>
+          <t>-91,65; -6,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -26,48</t>
+          <t>-95,06; -31,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 447,64</t>
+          <t>-82,1; 417,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 303,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 15,19</t>
+          <t>-76,86; 20,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,46; -4,91</t>
+          <t>-89,71; -9,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 5,48</t>
+          <t>-9,8; 5,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 0,0</t>
+          <t>-13,11; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,56</t>
+          <t>-5,63; 2,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 0,0</t>
+          <t>-7,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -1,05</t>
+          <t>-10,17; -1,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -1,52</t>
+          <t>-10,75; -2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,41</t>
+          <t>-2,06; 4,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,83</t>
+          <t>-3,33; 2,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 0,78</t>
+          <t>-4,52; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,43</t>
+          <t>-5,31; -0,16</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,32</t>
+          <t>-95,08; -0,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,64</t>
+          <t>-100,0; -16,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-89,27; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,72; 50,71</t>
+          <t>-79,93; 45,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,63; -2,58</t>
+          <t>-92,41; 17,78</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 4,63</t>
+          <t>-15,46; 3,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 1,3</t>
+          <t>-18,49; 0,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 0,0</t>
+          <t>-8,82; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,62</t>
+          <t>-5,92; 3,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 1,54</t>
+          <t>-8,36; 1,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 1,48</t>
+          <t>-7,75; 1,38</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 271,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 270,22</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,71</t>
+          <t>-7,67; -0,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -1,54</t>
+          <t>-8,47; -1,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,74</t>
+          <t>-2,78; 2,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,8</t>
+          <t>-3,32; 1,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,24</t>
+          <t>-3,83; 0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,56</t>
+          <t>-4,52; -0,51</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-91,65; -6,11</t>
+          <t>-90,95; -11,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,06; -31,45</t>
+          <t>-100,0; -29,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 417,53</t>
+          <t>-83,7; 354,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 303,06</t>
+          <t>-100,0; 394,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 20,78</t>
+          <t>-75,15; 29,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,71; -9,23</t>
+          <t>-88,43; -12,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,74; 5,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 5,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,56</t>
+          <t>-4,95; 2,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 0,0</t>
+          <t>-7,65; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-16,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-16,2%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-4,89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-5,26</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -1,02</t>
+          <t>-2,35; 4,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -2,0</t>
+          <t>-3,37; 2,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,64</t>
+          <t>-10,45; -1,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,16</t>
+          <t>-10,19; -1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,64</t>
+          <t>-4,85; 0,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -0,16</t>
+          <t>-5,51; -0,32</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>79,06%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-9,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-76,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-82,6%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-95,08; -0,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,27; —</t>
+          <t>-100,0; -13,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 23,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,93; 45,57</t>
+          <t>-81,2; 41,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,41; 17,78</t>
+          <t>-92,15; 1,25</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-3,9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-5,8</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 3,46</t>
+          <t>-9,74; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 0,47</t>
+          <t>-5,95; 3,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 0,0</t>
+          <t>-15,19; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,59</t>
+          <t>-18,17; 0,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,58</t>
+          <t>-7,99; 1,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,38</t>
+          <t>-7,34; 1,4</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,44%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-52,96%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-78,82%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-9,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-3,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-4,34</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,85</t>
+          <t>-2,19; 2,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -1,57</t>
+          <t>-3,33; 1,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,4</t>
+          <t>-7,41; -0,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,85</t>
+          <t>-8,43; -1,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,25</t>
+          <t>-3,88; 0,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,51</t>
+          <t>-4,52; -0,55</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-26,69%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-67,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-80,02%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-26,69%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -11,08</t>
+          <t>-74,55; 447,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,7; 354,81</t>
+          <t>-90,2; 0,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 394,89</t>
+          <t>-95,53; -26,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 29,56</t>
+          <t>-75,32; 15,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,43; -12,08</t>
+          <t>-88,46; -4,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,275 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.03012573615666387</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7393654624920608</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.0192907350501168</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3613146330950254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,74; 5,5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,05; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 2,56</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,65; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.914374444849952</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.115574747884181</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>-1.099218219939204</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.069047581646104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-16,2%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-17,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.436429525064975</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>0.6893266138012216</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-0.04074539275221738</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-0.05339040626412536</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,26</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 4,37</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,37; 2,16</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,45; -1,16</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,19; -1,69</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-4,85; 0,83</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; -0,32</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-9,78%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-76,79%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-82,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-43,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-67,41%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4149584590516583</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.005500252412065114</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8566882328968782</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.9859923736061131</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.1814903176766735</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.4632851313508615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -13,39</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 23,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-81,2; 41,28</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-92,15; 1,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.2800966208189179</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.5888012923136471</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.836574404967245</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.090301137341026</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.7575275993832512</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.046027906904655</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,9</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,4</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.227462134046755</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5594948287202645</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.003295388240779026</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.2735452967412053</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.458007659940375</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.005200894090591157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,74; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,95; 3,68</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-15,19; 3,39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-18,17; 0,49</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-7,99; 1,52</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,34; 1,4</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1.421934151053191</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.01884766191295894</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.6940677930830826</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.7988268362592553</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2483013117715297</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.6338316407798621</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,44%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-52,96%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-78,82%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-57,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-59,1%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>-0.9491136634588481</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7265618925136441</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9175695302627631</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>0.4432573288640664</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.02278530063200847</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.378254709086851</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2237254331750204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +876,293 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,66</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,59</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.4334211611180009</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.07989516387372436</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.00164385264363881</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.6129874495860419</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.2355405235130041</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.3586689125781709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,19; 2,82</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 1,42</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,41; -0,62</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-8,43; -1,65</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-3,88; 0,17</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; -0,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.171337567462212</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.384505690150018</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.385252308486131</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.308200010604004</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.249715134883353</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.31352159283019</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-26,69%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-67,5%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-80,02%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-44,79%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-65,27%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.7112248559524675</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.882670415296421</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.4087280496368149</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.7445494272077646</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.3556306623659186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-74,55; 447,64</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-90,2; 0,29</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-95,53; -26,48</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-75,32; 15,19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-88,46; -4,91</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1843360939452897</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.00172293006929783</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.6424751714096066</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3335113075089078</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5078537493788823</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.1695274355877142</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.09980826424660734</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5343034124500713</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.7478621087070263</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.1722125630448972</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.4143939045263949</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.368508224141349</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6287102907192618</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.257737747398537</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.472462489116984</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.6196136231248176</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.8765239645935529</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.7613507018380518</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.3749873362954599</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.1455554707515535</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.2467071504899816</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.2337764288028098</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.08095218661885072</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.4500635496993216</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2649722243507551</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.5353779017226349</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.7493660665602574</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2539013011452667</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.6109609524741155</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.7651201214232313</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.8698259525166574</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.9521101884455119</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.7015993865609904</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.8759654742298826</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5.003985905492915</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.608855272773712</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.4079745872833925</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.04917850258920684</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.5501440006570193</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.07576235200400294</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1170,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
